--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v2.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Viewpoint Elicitation</t>
+          <t>Active Listening</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Best Practise Benchmarking</t>
+          <t>Best Practice Benchmarking</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -820,16 +820,12 @@
         </is>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0.95</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>Compares project concepts against industry best‑practice examples of similar products to identify improvement opportunities.</t>
@@ -2295,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
@@ -2603,7 +2599,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Awareness Programme Development</t>
+          <t>Awareness Program Development</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2701,16 +2697,12 @@
         </is>
       </c>
       <c r="U17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+        <v>0.96</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>Designs, implements and updates organisation‑wide cyber security awareness programs in line with best practice.</t>
@@ -3655,7 +3647,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Practise Review</t>
+          <t>Practice Review</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4046,7 +4038,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Team Collabouration</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4136,16 +4128,12 @@
         </is>
       </c>
       <c r="U28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0.95</v>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
           <t>Collaborates with interdisciplinary teams to design and implement cyber security measures.</t>
@@ -4276,13 +4264,9 @@
         <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
           <t>Selects and operates suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
@@ -4932,7 +4916,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration</t>
+          <t>Device Configuration Setup</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5021,10 +5005,10 @@
         </is>
       </c>
       <c r="U36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
@@ -5728,7 +5712,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Risk Categorisation</t>
+          <t>Risk Categorisation Analysis</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5824,9 +5808,13 @@
         <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W42" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>postprocess: spelling/redundancy</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr">
         <is>
           <t>Assesses device data sensitivity to assign appropriate risk categories for security management.</t>
@@ -6882,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
@@ -7001,9 +6989,13 @@
         <v>1</v>
       </c>
       <c r="V51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W51" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>postprocess: spelling/redundancy</t>
+        </is>
+      </c>
       <c r="X51" t="inlineStr">
         <is>
           <t>Explores emerging digital tools to organise and analyse data and support effective communication.</t>
@@ -7156,7 +7148,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ICT Gap Identification</t>
+          <t>Ict Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7248,10 +7240,10 @@
         </is>
       </c>
       <c r="U53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
@@ -10480,7 +10472,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Anomaly Resolution</t>
+          <t>Blockchain Problem Solving</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -10570,10 +10562,10 @@
         </is>
       </c>
       <c r="U80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr">
@@ -12782,13 +12774,9 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr">
         <is>
           <t>Compiles alerts, logs and event reports into structured datasets in line with organisational policies.</t>
@@ -12822,7 +12810,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>False Positive Detection</t>
+          <t>False Data Detection</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -12919,10 +12907,10 @@
         </is>
       </c>
       <c r="U98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V98" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr">
@@ -13582,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
@@ -15394,7 +15382,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Assessment Evaluation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -15481,10 +15469,10 @@
         </is>
       </c>
       <c r="U118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr">
@@ -16168,7 +16156,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Security Anomaly Identification</t>
+          <t>Problem Solving in Security</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -16268,9 +16256,13 @@
         <v>1</v>
       </c>
       <c r="V124" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W124" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>postprocess: spelling/redundancy</t>
+        </is>
+      </c>
       <c r="X124" t="inlineStr">
         <is>
           <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
@@ -16400,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr">
@@ -16664,7 +16656,7 @@
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr">
@@ -17064,7 +17056,7 @@
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr">
@@ -17939,7 +17931,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Response Plan Evaluation</t>
+          <t>Incident Response Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -18045,10 +18037,10 @@
         </is>
       </c>
       <c r="U137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
@@ -18621,10 +18613,10 @@
         </is>
       </c>
       <c r="U141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
@@ -18922,7 +18914,7 @@
         <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
@@ -20920,7 +20912,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Team Collabouration</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -21019,16 +21011,12 @@
         </is>
       </c>
       <c r="U158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V158" t="n">
         <v>0.95</v>
       </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+      <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr">
         <is>
           <t>Collaborates with team members using communication tools and strategies to maintain effective working relationships.</t>

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v2.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Active Listening</t>
+          <t>Viewpoint Elicitation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
@@ -2163,9 +2163,13 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>postprocess: spelling/redundancy</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
           <t>Iteratively refines and finalises solutions to meet specific task requirements.</t>
@@ -2291,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
@@ -2463,7 +2467,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Team Facilitation</t>
+          <t>Discussion Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2560,10 +2564,10 @@
         </is>
       </c>
       <c r="U16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
@@ -2700,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
@@ -2736,7 +2740,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Clear Technical Writing</t>
+          <t>Cyber Security Writing</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2822,10 +2826,10 @@
         </is>
       </c>
       <c r="U18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
@@ -2861,7 +2865,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Current Awareness Assessment</t>
+          <t>Cyber Security Awareness Assessment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2955,10 +2959,10 @@
         </is>
       </c>
       <c r="U19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
@@ -2994,7 +2998,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Improvement Communication</t>
+          <t>Improvement Requirements Communication</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3080,10 +3084,10 @@
         </is>
       </c>
       <c r="U20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
@@ -3381,7 +3385,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Outcome Documentation</t>
+          <t>Review Outcome Documentation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3475,10 +3479,10 @@
         </is>
       </c>
       <c r="U23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
@@ -3514,7 +3518,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Policy Contribution Drafting</t>
+          <t>Policy Drafting</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3608,10 +3612,10 @@
         </is>
       </c>
       <c r="U24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
@@ -4264,9 +4268,13 @@
         <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W29" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>postprocess: spelling/redundancy</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
           <t>Selects and operates suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
@@ -5044,7 +5052,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Device Encryption Implementation</t>
+          <t>Device Encryption</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5133,10 +5141,10 @@
         </is>
       </c>
       <c r="U37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
@@ -5312,7 +5320,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Gap Analysis Evaluation</t>
+          <t>Best Practice Gap Analysis</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5409,10 +5417,10 @@
         </is>
       </c>
       <c r="U39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
@@ -5712,7 +5720,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Risk Categorisation Analysis</t>
+          <t>Risk Categorisation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5808,13 +5816,9 @@
         <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
           <t>Assesses device data sensitivity to assign appropriate risk categories for security management.</t>
@@ -6256,7 +6260,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Trend Monitoring</t>
+          <t>Security Development Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6349,10 +6353,10 @@
         </is>
       </c>
       <c r="U46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
@@ -6870,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
@@ -7029,7 +7033,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Evaluation Documentation Preparation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7109,10 +7113,10 @@
         </is>
       </c>
       <c r="U52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
@@ -12278,7 +12282,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Analytic Platform Operation</t>
+          <t>Data Log Ingestion</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -12371,10 +12375,10 @@
         </is>
       </c>
       <c r="U94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V94" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr">
@@ -12774,9 +12778,13 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W97" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>postprocess: spelling/redundancy</t>
+        </is>
+      </c>
       <c r="X97" t="inlineStr">
         <is>
           <t>Compiles alerts, logs and event reports into structured datasets in line with organisational policies.</t>
@@ -13210,7 +13218,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Risk Likelihood Assessment</t>
+          <t>Threat Risk Assessment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -13303,10 +13311,10 @@
         </is>
       </c>
       <c r="U101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V101" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr">
@@ -13570,7 +13578,7 @@
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
@@ -16028,7 +16036,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Industry Methodology Research</t>
+          <t>Security Architecture Methodology Research</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -16117,10 +16125,10 @@
         </is>
       </c>
       <c r="U123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V123" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
@@ -16296,7 +16304,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Security Architecture Documentation</t>
+          <t>Security Requirements Documentation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -16389,10 +16397,10 @@
         </is>
       </c>
       <c r="U125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V125" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr">
@@ -16656,7 +16664,7 @@
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr">
@@ -17056,7 +17064,7 @@
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr">
@@ -17364,7 +17372,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Technical Specification Reading</t>
+          <t>Technical Documentation Reading</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -17457,10 +17465,10 @@
         </is>
       </c>
       <c r="U133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V133" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr">
@@ -17931,7 +17939,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Incident Response Evaluation</t>
+          <t>Response Plan Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -18037,10 +18045,10 @@
         </is>
       </c>
       <c r="U137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V137" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
@@ -18914,7 +18922,7 @@
         <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
@@ -18950,7 +18958,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Security Policy Development</t>
+          <t>Incident Management Policy Development</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -19060,10 +19068,10 @@
         </is>
       </c>
       <c r="U144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V144" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
@@ -20080,7 +20088,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Numerical Data Analysis</t>
+          <t>Business Data Analysis</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -20179,10 +20187,10 @@
         </is>
       </c>
       <c r="U152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V152" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr">
@@ -20774,7 +20782,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategic Planning</t>
+          <t>Priority Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -20873,10 +20881,10 @@
         </is>
       </c>
       <c r="U157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V157" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v2.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Viewpoint Elicitation</t>
+          <t>Stakeholder Viewpoint Elicitation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Research Information Gathering</t>
+          <t>Information Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="U11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
@@ -2163,13 +2163,9 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>Iteratively refines and finalises solutions to meet specific task requirements.</t>
@@ -2740,7 +2736,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cyber Security Writing</t>
+          <t>Clear Technical Writing</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2826,10 +2822,10 @@
         </is>
       </c>
       <c r="U18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
@@ -2865,7 +2861,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cyber Security Awareness Assessment</t>
+          <t>Current Awareness Assessment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2959,10 +2955,10 @@
         </is>
       </c>
       <c r="U19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
@@ -2998,7 +2994,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Improvement Requirements Communication</t>
+          <t>Improvement Communication</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3084,10 +3080,10 @@
         </is>
       </c>
       <c r="U20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
@@ -3216,13 +3212,9 @@
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
@@ -3385,7 +3377,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Review Outcome Documentation</t>
+          <t>Outcome Documentation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3479,10 +3471,10 @@
         </is>
       </c>
       <c r="U23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
@@ -4924,7 +4916,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration Setup</t>
+          <t>Device Configuration</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5013,10 +5005,10 @@
         </is>
       </c>
       <c r="U36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
@@ -5052,7 +5044,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Device Encryption</t>
+          <t>Device Encryption Implementation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5141,10 +5133,10 @@
         </is>
       </c>
       <c r="U37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
@@ -5320,7 +5312,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Best Practice Gap Analysis</t>
+          <t>Gap Analysis Evaluation</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5417,10 +5409,10 @@
         </is>
       </c>
       <c r="U39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
@@ -5852,7 +5844,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Communication</t>
+          <t>Physical Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5949,10 +5941,10 @@
         </is>
       </c>
       <c r="U43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
@@ -7033,7 +7025,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Evaluation Documentation Preparation</t>
+          <t>Documentation Preparation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7113,10 +7105,10 @@
         </is>
       </c>
       <c r="U52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
@@ -7537,7 +7529,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>Financial Impact Assessment</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7617,10 +7609,10 @@
         </is>
       </c>
       <c r="U56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
@@ -12778,13 +12770,9 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr">
         <is>
           <t>Compiles alerts, logs and event reports into structured datasets in line with organisational policies.</t>
@@ -13878,7 +13866,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Anomaly Detection Troubleshooting</t>
+          <t>Anomaly Detection</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -13965,10 +13953,10 @@
         </is>
       </c>
       <c r="U106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V106" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr">
@@ -15390,7 +15378,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Assessment Evaluation</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -15477,10 +15465,10 @@
         </is>
       </c>
       <c r="U118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V118" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr">
@@ -15768,7 +15756,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data Classification Identification</t>
+          <t>Data Type Identification</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -15865,10 +15853,10 @@
         </is>
       </c>
       <c r="U121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V121" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr">
@@ -16036,7 +16024,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Security Architecture Methodology Research</t>
+          <t>Industry Methodology Research</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -16125,10 +16113,10 @@
         </is>
       </c>
       <c r="U123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
@@ -16164,7 +16152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Problem Solving in Security</t>
+          <t>Security Contextual Problem Solving</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -16264,13 +16252,9 @@
         <v>1</v>
       </c>
       <c r="V124" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>postprocess: spelling/redundancy</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr">
         <is>
           <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
@@ -17372,7 +17356,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Technical Documentation Reading</t>
+          <t>Technical Specification Reading</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -17465,10 +17449,10 @@
         </is>
       </c>
       <c r="U133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr">
@@ -17939,7 +17923,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Response Plan Evaluation</t>
+          <t>Incident Response Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -18045,10 +18029,10 @@
         </is>
       </c>
       <c r="U137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
@@ -18515,7 +18499,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Response Communication Assessment</t>
+          <t>Communication Effectiveness Assessment</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -18621,10 +18605,10 @@
         </is>
       </c>
       <c r="U141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V141" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
@@ -18660,7 +18644,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Data Analysis</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -18770,10 +18754,10 @@
         </is>
       </c>
       <c r="U142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V142" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
@@ -18958,7 +18942,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Incident Management Policy Development</t>
+          <t>Security Policy Development</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -19068,10 +19052,10 @@
         </is>
       </c>
       <c r="U144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
@@ -20506,7 +20490,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -20605,10 +20589,10 @@
         </is>
       </c>
       <c r="U155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V155" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr">
@@ -20782,7 +20766,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Priority Planning</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -20881,10 +20865,10 @@
         </is>
       </c>
       <c r="U157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V157" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v2.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA160"/>
+  <dimension ref="A1:AB160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,20 +548,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>consensus_votes</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>org_description</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>description_changed</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>org_keywords</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>keywords_changed</t>
         </is>
@@ -685,21 +690,30 @@
       <c r="V2" t="n">
         <v>0.9</v>
       </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>keep:0, "Stakeholder Viewpoint Elicitation":5</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>Elicits others’ views and integrates feedback to refine ideas during collaborative discussions.</t>
         </is>
       </c>
-      <c r="Y2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>communication, empathy, feedback, stakeholder engagement, interpersonal skills</t>
         </is>
       </c>
-      <c r="AA2" t="b">
+      <c r="AB2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -828,18 +842,23 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>Compares project concepts against industry best‑practice examples of similar products to identify improvement opportunities.</t>
         </is>
       </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>benchmarking, best practice, performance metrics, competitive analysis, industry standards</t>
         </is>
       </c>
-      <c r="AA3" t="b">
+      <c r="AB3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -965,21 +984,30 @@
       <c r="V4" t="n">
         <v>0.9</v>
       </c>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>keep:0, "Idea Generation":5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Generates diverse solutions by leading focused brainstorming sessions to address identified issues.</t>
         </is>
       </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>ideation, creative problem solving, mind mapping, group facilitation, innovation techniques</t>
         </is>
       </c>
-      <c r="AA4" t="b">
+      <c r="AB4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1108,18 +1136,23 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>Applies systematic analytical methods to collect and assess concepts in complex, non‑routine scenarios.</t>
         </is>
       </c>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>analytical methodology, systematic concept evaluation, ideation processes, feasibility analysis, design thinking</t>
         </is>
       </c>
-      <c r="AA5" t="b">
+      <c r="AB5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1236,18 +1269,23 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>Applies creative thinking techniques to develop innovative solutions to workplace challenges.</t>
         </is>
       </c>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
         </is>
       </c>
-      <c r="AA6" t="b">
+      <c r="AB6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1364,18 +1402,23 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>Records and formats feedback in line with organisational standards to ensure consistent documentation.</t>
         </is>
       </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>record‑keeping, compliance, audit trail, quality assurance, organisational standards</t>
         </is>
       </c>
-      <c r="AA7" t="b">
+      <c r="AB7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1493,21 +1536,30 @@
       <c r="V8" t="n">
         <v>0.9</v>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
+          <t>keep:0, "Idea Viability Evaluation":5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>Assesses ideas by systematically comparing them against identified viability factors.</t>
         </is>
       </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>feasibility analysis, risk assessment, criteria weighting, business case evaluation, market viability</t>
         </is>
       </c>
-      <c r="AA8" t="b">
+      <c r="AB8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1636,18 +1688,23 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>Collaborates with relevant personnel to identify and select consultation issues for focused analysis.</t>
         </is>
       </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>stakeholder engagement, problem identification, needs assessment, consultation processes, decision‑making</t>
         </is>
       </c>
-      <c r="AA9" t="b">
+      <c r="AB9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1768,18 +1825,23 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>Drafts detailed proposals and plans using sector‑specific terminology for stakeholder review.</t>
         </is>
       </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>stakeholder communication, business case development, grant and RFP responses, technical documentation, persuasive writing</t>
         </is>
       </c>
-      <c r="AA10" t="b">
+      <c r="AB10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1799,7 +1861,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Information Research</t>
+          <t>Research Information Gathering</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1888,26 +1950,31 @@
         </is>
       </c>
       <c r="U11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>keep:4, "Information Research":1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Gathers and evaluates relevant data to identify viable solutions to the identified issue.</t>
         </is>
       </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
         </is>
       </c>
-      <c r="AA11" t="b">
+      <c r="AB11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2032,18 +2099,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>Selects appropriate solution formats and delivers tailored presentations to stakeholders.</t>
         </is>
       </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>stakeholder communication, visual presentation tools, solution pitching, format selection, business briefings</t>
         </is>
       </c>
-      <c r="AA12" t="b">
+      <c r="AB12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2165,21 +2237,30 @@
       <c r="V13" t="n">
         <v>0.9</v>
       </c>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
+          <t>keep:0, "Solution Refinement":5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>Iteratively refines and finalises solutions to meet specific task requirements.</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>requirements analysis, design optimisation, prototype testing, continuous improvement, validation feedback</t>
         </is>
       </c>
-      <c r="AA13" t="b">
+      <c r="AB13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2296,18 +2377,23 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Evaluates alternative solutions to a business problem, identifying constraints to determine feasible options.</t>
         </is>
       </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
         </is>
       </c>
-      <c r="AA14" t="b">
+      <c r="AB14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2432,18 +2518,23 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>Proactively seeks stakeholder input on ideas to refine concepts and align expectations.</t>
         </is>
       </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>stakeholder engagement, feedback collection, surveys, interviews, communication</t>
         </is>
       </c>
-      <c r="AA15" t="b">
+      <c r="AB15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2565,21 +2656,30 @@
       <c r="V16" t="n">
         <v>0.9</v>
       </c>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
+          <t>keep:0, "Discussion Facilitation":5</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Guides group discussions, encourages participation and coordinates tasks to achieve shared outcomes.</t>
         </is>
       </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>group dynamics, collaboration tools, meeting facilitation, conflict resolution, consensus building</t>
         </is>
       </c>
-      <c r="AA16" t="b">
+      <c r="AB16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2705,18 +2805,23 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>Designs, implements and updates organisation‑wide cyber security awareness programs in line with best practice.</t>
         </is>
       </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>cyber security, security awareness training, risk management, phishing simulations, compliance governance</t>
         </is>
       </c>
-      <c r="AA17" t="b">
+      <c r="AB17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2830,18 +2935,23 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Writes workplace documents using precise cyber security terminology to clearly convey technical information.</t>
         </is>
       </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>cyber security terminology, technical documentation, information security policies, industry standards (ISO 27001, NIST), risk assessment reporting</t>
         </is>
       </c>
-      <c r="AA18" t="b">
+      <c r="AB18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2963,18 +3073,23 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>Assesses cyber security awareness within the work area through surveys and interviews to establish baseline levels.</t>
         </is>
       </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>cyber security, risk awareness, security posture, threat intelligence, security metrics</t>
         </is>
       </c>
-      <c r="AA19" t="b">
+      <c r="AB19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3083,23 +3198,28 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
+          <t>keep:3, "Improvement Requirements Communication":1, "Outcome and Improvement Communication":1</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
           <t>Communicates review results and cyber security improvement needs in accordance with organisational policies and procedures.</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
         </is>
       </c>
-      <c r="AA20" t="b">
+      <c r="AB20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3214,21 +3334,30 @@
       <c r="V21" t="n">
         <v>0.9</v>
       </c>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
+          <t>keep:0, "Insight Presentation":5</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
           <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
         </is>
       </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>stakeholder communication, knowledge transfer, visual storytelling, training briefings, presentation tools</t>
         </is>
       </c>
-      <c r="AA21" t="b">
+      <c r="AB21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3346,18 +3475,23 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
           <t>Interprets Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
         </is>
       </c>
-      <c r="AA22" t="b">
+      <c r="AB22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3479,18 +3613,23 @@
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
           <t>Prepares detailed review outcome reports outlining improvement recommendations for relevant personnel.</t>
         </is>
       </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>reporting, review outcomes, improvement recommendations, stakeholder communication, record‑keeping</t>
         </is>
       </c>
-      <c r="AA23" t="b">
+      <c r="AB23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3609,21 +3748,30 @@
       <c r="V24" t="n">
         <v>0.9</v>
       </c>
-      <c r="W24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/5: </t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr">
         <is>
+          <t>keep:0, "Policy Drafting":4, "Policy Development":1</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
           <t>Drafts cyber security policies and procedures and disseminates them to relevant staff.</t>
         </is>
       </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>cyber security governance, policy development, risk management, compliance frameworks, stakeholder communication</t>
         </is>
       </c>
-      <c r="AA24" t="b">
+      <c r="AB24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3742,21 +3890,30 @@
       <c r="V25" t="n">
         <v>0.9</v>
       </c>
-      <c r="W25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr">
         <is>
+          <t>keep:0, "Practice Review":5</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
           <t>Conducts systematic reviews of cyber security practices to ensure alignment with organisational policies and procedures.</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>cyber security, policy compliance, risk assessment, security governance, audit controls</t>
         </is>
       </c>
-      <c r="AA25" t="b">
+      <c r="AB25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3878,18 +4035,23 @@
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
           <t>Maintains up‑to‑date cyber security protection records by organising and documenting relevant data.</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>cyber security documentation, information security records, compliance logging, data governance, audit trail management</t>
         </is>
       </c>
-      <c r="AA26" t="b">
+      <c r="AB26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4003,18 +4165,23 @@
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
           <t>Engages relevant stakeholders through meetings and surveys to gather input that informs decision‑making.</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
         </is>
       </c>
-      <c r="AA27" t="b">
+      <c r="AB27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4132,18 +4299,23 @@
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
           <t>Collaborates with interdisciplinary teams to design and implement cyber security measures.</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="inlineStr">
         <is>
           <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, collaboration tools</t>
         </is>
       </c>
-      <c r="AA28" t="b">
+      <c r="AB28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4269,18 +4441,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
           <t>Selects and operates suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
         </is>
       </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="inlineStr">
         <is>
           <t>cyber security, security platforms, SIEM, threat monitoring, information security</t>
         </is>
       </c>
-      <c r="AA29" t="b">
+      <c r="AB29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4402,18 +4579,23 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
           <t>Analyses current cyber threat reports to assess organisational impacts and advise on security measures.</t>
         </is>
       </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>cyber security, threat intelligence, trend monitoring, vulnerability assessment, security analytics</t>
         </is>
       </c>
-      <c r="AA30" t="b">
+      <c r="AB30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4539,18 +4721,23 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
           <t>Coordinates training sessions and information updates by scheduling, delivering and recording activities.</t>
         </is>
       </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="inlineStr">
         <is>
           <t>training schedules, learning management systems, record management, information updates, training logistics</t>
         </is>
       </c>
-      <c r="AA31" t="b">
+      <c r="AB31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4585,11 +4772,12 @@
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="b">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="b">
         <v>1</v>
       </c>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="b">
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4624,11 +4812,12 @@
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="b">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="b">
         <v>1</v>
       </c>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="b">
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4753,18 +4942,23 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
           <t>Installs and configures up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
         </is>
       </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="inlineStr">
+      <c r="Z34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="inlineStr">
         <is>
           <t>cyber security, endpoint protection, malware scanning, signature updates, security hygiene</t>
         </is>
       </c>
-      <c r="AA34" t="b">
+      <c r="AB34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4885,18 +5079,23 @@
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
           <t>Analyses breach volumes and assesses business impacts across review periods to inform risk mitigation.</t>
         </is>
       </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="inlineStr">
+      <c r="Z35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="inlineStr">
         <is>
           <t>risk assessment, incident tracking, business impact analysis, compliance reporting, security metrics</t>
         </is>
       </c>
-      <c r="AA35" t="b">
+      <c r="AB35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5010,21 +5209,30 @@
       <c r="V36" t="n">
         <v>0.9</v>
       </c>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
+          <t>keep:0, "Device Configuration":5</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
           <t>Performs initial device set‑up by updating firmware and configuring settings on new devices.</t>
         </is>
       </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="inlineStr">
+      <c r="Z36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="inlineStr">
         <is>
           <t>device provisioning, firmware updates, configuration management, hardware initialisation, system onboarding</t>
         </is>
       </c>
-      <c r="AA36" t="b">
+      <c r="AB36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5141,18 +5349,23 @@
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
           <t>Implements device encryption in accordance with prescribed procedures to secure hardware.</t>
         </is>
       </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="inlineStr">
+      <c r="Z37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="inlineStr">
         <is>
           <t>encryption, device security, endpoint encryption, mobile device management, cryptography</t>
         </is>
       </c>
-      <c r="AA37" t="b">
+      <c r="AB37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5281,18 +5494,23 @@
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
           <t>Creates and updates a register of networked devices to support inventory tracking and asset management.</t>
         </is>
       </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="inlineStr">
+      <c r="Z38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="inlineStr">
         <is>
           <t>IT asset tracking, hardware registers, network inventories, CMDB, asset management software</t>
         </is>
       </c>
-      <c r="AA38" t="b">
+      <c r="AB38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5417,18 +5635,23 @@
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
           <t>Conducts gap analyses to assess and benchmark best‑practice implementation effectiveness.</t>
         </is>
       </c>
-      <c r="Y39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="inlineStr">
+      <c r="Z39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>benchmarking, performance metrics, best‑practice assessment, process improvement, effectiveness evaluation</t>
         </is>
       </c>
-      <c r="AA39" t="b">
+      <c r="AB39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5545,18 +5768,23 @@
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
           <t>Generates robust, unique passwords for personal and work accounts in line with approved complexity criteria.</t>
         </is>
       </c>
-      <c r="Y40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="inlineStr">
+      <c r="Z40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="inlineStr">
         <is>
           <t>authentication, password complexity, entropy, cyber security, password managers</t>
         </is>
       </c>
-      <c r="AA40" t="b">
+      <c r="AB40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5681,18 +5909,23 @@
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
           <t>Develops comprehensive physical security plans and disseminates them organisation‑wide to ensure coordinated protection.</t>
         </is>
       </c>
-      <c r="Y41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr">
         <is>
           <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
         </is>
       </c>
-      <c r="AA41" t="b">
+      <c r="AB41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5712,7 +5945,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Risk Categorisation</t>
+          <t>Data Risk Categorisation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5810,21 +6043,30 @@
       <c r="V42" t="n">
         <v>0.9</v>
       </c>
-      <c r="W42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr">
         <is>
+          <t>keep:0, "Data Risk Categorisation/Risk Categorisation":5</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
           <t>Assesses device data sensitivity to assign appropriate risk categories for security management.</t>
         </is>
       </c>
-      <c r="Y42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="inlineStr">
         <is>
           <t>risk assessment, information sensitivity, device classification, cyber security, risk matrices</t>
         </is>
       </c>
-      <c r="AA42" t="b">
+      <c r="AB42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5946,21 +6188,30 @@
       <c r="V43" t="n">
         <v>0.9</v>
       </c>
-      <c r="W43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X43" t="inlineStr">
         <is>
+          <t>keep:0, "Physical Security Plan Communication":5</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
           <t>Delivers organisation‑wide briefings on physical security plans to support understanding and compliance.</t>
         </is>
       </c>
-      <c r="Y43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr">
         <is>
           <t>physical security, risk assessment, security policy, stakeholder communication, access control</t>
         </is>
       </c>
-      <c r="AA43" t="b">
+      <c r="AB43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6085,18 +6336,23 @@
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
           <t>Selects appropriate security protocols for each device to mitigate identified risk levels.</t>
         </is>
       </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="inlineStr">
+      <c r="Z44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="inlineStr">
         <is>
           <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
         </is>
       </c>
-      <c r="AA44" t="b">
+      <c r="AB44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6221,18 +6477,23 @@
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
           <t>Advises the organisation by evaluating options and recommending optimal security strategies.</t>
         </is>
       </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="inlineStr">
         <is>
           <t>cyber security governance, risk assessment, security frameworks, threat modelling, ISO 27001</t>
         </is>
       </c>
-      <c r="AA45" t="b">
+      <c r="AB45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6350,21 +6611,30 @@
       <c r="V46" t="n">
         <v>0.9</v>
       </c>
-      <c r="W46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X46" t="inlineStr">
         <is>
+          <t>keep:0, "Security Development Monitoring":5</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
           <t>Monitors emerging digital security developments to inform risk assessments and protective measures.</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="inlineStr">
+      <c r="Z46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="inlineStr">
         <is>
           <t>cyber security, threat intelligence, vulnerability tracking, security intelligence feeds, digital risk monitoring</t>
         </is>
       </c>
-      <c r="AA46" t="b">
+      <c r="AB46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6489,18 +6759,23 @@
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
           <t>Installs and configures software patches on desktop and mobile devices to maintain system security.</t>
         </is>
       </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="inlineStr">
+      <c r="Z47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="inlineStr">
         <is>
           <t>patch management, software updates, endpoint management, mobile device management, security patches</t>
         </is>
       </c>
-      <c r="AA47" t="b">
+      <c r="AB47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6629,18 +6904,23 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
           <t>Enables multi‑factor authentication on supported systems to strengthen account security.</t>
         </is>
       </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="inlineStr">
+      <c r="Z48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="inlineStr">
         <is>
           <t>multi‑factor authentication, MFA, OTP, access control, cyber security</t>
         </is>
       </c>
-      <c r="AA48" t="b">
+      <c r="AB48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6748,18 +7028,23 @@
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
           <t>Develops detailed action plans aligned with policies, prioritising tasks and scheduling implementation.</t>
         </is>
       </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="inlineStr">
+      <c r="Z49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="inlineStr">
         <is>
           <t>project scheduling, prioritisation, policy compliance, change management, implementation planning</t>
         </is>
       </c>
-      <c r="AA49" t="b">
+      <c r="AB49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6871,18 +7156,23 @@
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
           <t>Ranks proposed changes to clarify improvement opportunities and inform implementation scheduling.</t>
         </is>
       </c>
-      <c r="Y50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="inlineStr">
+      <c r="Z50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="inlineStr">
         <is>
           <t>change management, prioritisation, opportunity assessment, implementation scheduling, project planning</t>
         </is>
       </c>
-      <c r="AA50" t="b">
+      <c r="AB50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6994,18 +7284,23 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
           <t>Explores emerging digital tools to organise and analyse data and support effective communication.</t>
         </is>
       </c>
-      <c r="Y51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="inlineStr">
+      <c r="Z51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="inlineStr">
         <is>
           <t>data management, digital collaboration tools, emerging technologies, cloud computing, data visualisation</t>
         </is>
       </c>
-      <c r="AA51" t="b">
+      <c r="AB51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7025,7 +7320,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Evaluation Documentation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7105,26 +7400,35 @@
         </is>
       </c>
       <c r="U52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W52" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/5: </t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr">
         <is>
+          <t>keep:1, "Evaluation Documentation":3, "Evaluation Documentation Preparation":1</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>Prepares evaluation documents, organises findings and submits them to a supervisor for review.</t>
         </is>
       </c>
-      <c r="Y52" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="inlineStr">
+      <c r="Z52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr">
         <is>
           <t>technical writing, document review, quality assurance, reporting standards, document control</t>
         </is>
       </c>
-      <c r="AA52" t="b">
+      <c r="AB52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7244,18 +7548,23 @@
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
           <t>Analyses strategic objectives against current ICT capability in hybrid environments to identify gaps and propose improvements.</t>
         </is>
       </c>
-      <c r="Y53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="inlineStr">
+      <c r="Z53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="inlineStr">
         <is>
           <t>gap analysis, strategic alignment, technology roadmaps, ICT governance, digital transformation</t>
         </is>
       </c>
-      <c r="AA53" t="b">
+      <c r="AB53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7379,18 +7688,23 @@
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>Assesses proposed ICT system changes in hybrid environments for alignment with organisational strategic objectives.</t>
         </is>
       </c>
-      <c r="Y54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="inlineStr">
+      <c r="Z54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="inlineStr">
         <is>
           <t>impact assessment, ICT systems, strategic alignment, change management, performance metrics</t>
         </is>
       </c>
-      <c r="AA54" t="b">
+      <c r="AB54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7498,18 +7812,23 @@
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
           <t>Researches and tests innovative ideas, applying findings to refine work practices and processes.</t>
         </is>
       </c>
-      <c r="Y55" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="inlineStr">
+      <c r="Z55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="inlineStr">
         <is>
           <t>continuous improvement, process optimisation, ideation techniques, creative problem solving, innovation management</t>
         </is>
       </c>
-      <c r="AA55" t="b">
+      <c r="AB55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7529,7 +7848,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Financial Impact Assessment</t>
+          <t>Numerical Data Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7609,26 +7928,31 @@
         </is>
       </c>
       <c r="U56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>0.9</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
+          <t>keep:3, "Financial Impact Interpretation":2</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
           <t>Analyses numerical data and calculates financial impacts of proposed changes in hybrid environments.</t>
         </is>
       </c>
-      <c r="Y56" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="inlineStr">
+      <c r="Z56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="inlineStr">
         <is>
           <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, statistical calculations</t>
         </is>
       </c>
-      <c r="AA56" t="b">
+      <c r="AB56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7736,18 +8060,23 @@
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
           <t>Assesses policy compliance by documenting standards, targets and implementation approaches within action plans.</t>
         </is>
       </c>
-      <c r="Y57" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="inlineStr">
+      <c r="Z57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="inlineStr">
         <is>
           <t>regulatory standards, compliance frameworks, risk assessment, governance risk and compliance, policy implementation planning</t>
         </is>
       </c>
-      <c r="AA57" t="b">
+      <c r="AB57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7855,18 +8184,23 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
           <t>Develops detailed action plans with prioritised schedules to implement change initiatives efficiently.</t>
         </is>
       </c>
-      <c r="Y58" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="inlineStr">
+      <c r="Z58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="inlineStr">
         <is>
           <t>action planning, prioritised schedules, timeline management, resource allocation, critical path</t>
         </is>
       </c>
-      <c r="AA58" t="b">
+      <c r="AB58" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7974,18 +8308,23 @@
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
           <t>Assesses the complexity of ICT system changes and plans risk mitigation strategies across hybrid environments.</t>
         </is>
       </c>
-      <c r="Y59" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="inlineStr">
+      <c r="Z59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="inlineStr">
         <is>
           <t>ICT systems, change management, implementation complexity, risk analysis, impact assessment</t>
         </is>
       </c>
-      <c r="AA59" t="b">
+      <c r="AB59" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8105,18 +8444,23 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
           <t>Prepares concise reports outlining changes, gaps and improvement opportunities for senior staff.</t>
         </is>
       </c>
-      <c r="Y60" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="inlineStr">
+      <c r="Z60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="inlineStr">
         <is>
           <t>executive communication, gap analysis, change management, improvement recommendations, business reporting</t>
         </is>
       </c>
-      <c r="AA60" t="b">
+      <c r="AB60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8240,18 +8584,23 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
           <t>Analyses the organisation’s strategic plan against the industry environment and objectives, documenting findings.</t>
         </is>
       </c>
-      <c r="Y61" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="inlineStr">
+      <c r="Z61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="inlineStr">
         <is>
           <t>strategic alignment, industry benchmarking, SWOT analysis, organisational objectives, gap analysis</t>
         </is>
       </c>
-      <c r="AA61" t="b">
+      <c r="AB61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8359,18 +8708,23 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
           <t>Uses structured analytical frameworks to evaluate options and resolve complex, non‑routine problems.</t>
         </is>
       </c>
-      <c r="Y62" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="inlineStr">
+      <c r="Z62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="inlineStr">
         <is>
           <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
         </is>
       </c>
-      <c r="AA62" t="b">
+      <c r="AB62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8478,18 +8832,23 @@
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
           <t>Translates technical terminology into plain English to support understanding across diverse staff groups.</t>
         </is>
       </c>
-      <c r="Y63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="inlineStr">
+      <c r="Z63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="inlineStr">
         <is>
           <t>plain language, jargon translation, stakeholder communication, technical writing, audience adaptation</t>
         </is>
       </c>
-      <c r="AA63" t="b">
+      <c r="AB63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8600,18 +8959,23 @@
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
           <t>Analyses complex legislative material to assess compliance with organisational standards.</t>
         </is>
       </c>
-      <c r="Y64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="inlineStr">
+      <c r="Z64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="inlineStr">
         <is>
           <t>legislative compliance, policy analysis, regulatory standards, qualitative analysis</t>
         </is>
       </c>
-      <c r="AA64" t="b">
+      <c r="AB64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8722,18 +9086,23 @@
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
           <t>Evaluates organisational privacy policies against industry standards to ensure compliance in hybrid environments.</t>
         </is>
       </c>
-      <c r="Y65" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="inlineStr">
+      <c r="Z65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="inlineStr">
         <is>
           <t>privacy policy, regulatory standards, risk assessment, audit, data protection</t>
         </is>
       </c>
-      <c r="AA65" t="b">
+      <c r="AB65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8844,18 +9213,23 @@
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
           <t>Reviews ethical practices and feedback and applies the organisational code of ethics to guide decisions.</t>
         </is>
       </c>
-      <c r="Y66" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="inlineStr">
+      <c r="Z66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="inlineStr">
         <is>
           <t>professional ethics, codes of conduct, compliance, organisational governance, ethical frameworks</t>
         </is>
       </c>
-      <c r="AA66" t="b">
+      <c r="AB66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8966,18 +9340,23 @@
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
           <t>Collects and addresses feedback on review and grievance documentation from designated personnel.</t>
         </is>
       </c>
-      <c r="Y67" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="inlineStr">
+      <c r="Z67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="inlineStr">
         <is>
           <t>grievance procedures, review processes, stakeholder communication, document management, complaint handling</t>
         </is>
       </c>
-      <c r="AA67" t="b">
+      <c r="AB67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9088,18 +9467,23 @@
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
           <t>Conducts industry‑standard tests to assess information integrity, confidentiality, security and availability.</t>
         </is>
       </c>
-      <c r="Y68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="inlineStr">
+      <c r="Z68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="inlineStr">
         <is>
           <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, security controls</t>
         </is>
       </c>
-      <c r="AA68" t="b">
+      <c r="AB68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9210,18 +9594,23 @@
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
           <t>Synthesises diverse sources into cohesive written reports using specialised terminology and supporting documentation.</t>
         </is>
       </c>
-      <c r="Y69" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="inlineStr">
+      <c r="Z69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="inlineStr">
         <is>
           <t>literature review, source integration, technical writing, citation management, knowledge synthesis</t>
         </is>
       </c>
-      <c r="AA69" t="b">
+      <c r="AB69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9332,18 +9721,23 @@
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>Analyses and interprets intellectual property and copyright legislation to ensure organisational compliance.</t>
         </is>
       </c>
-      <c r="Y70" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="inlineStr">
+      <c r="Z70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="inlineStr">
         <is>
           <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
         </is>
       </c>
-      <c r="AA70" t="b">
+      <c r="AB70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9449,23 +9843,28 @@
         <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>0.95</v>
+        <v>0.9259999999999999</v>
       </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
           <t>Delivers updated policies, procedures and ethics documentation to designated personnel.</t>
         </is>
       </c>
-      <c r="Y71" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="inlineStr">
+      <c r="Z71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="inlineStr">
         <is>
           <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
         </is>
       </c>
-      <c r="AA71" t="b">
+      <c r="AB71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9576,18 +9975,23 @@
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
           <t>Updates privacy policies, procedures and codes of ethics to reflect current legislation and compliance requirements.</t>
         </is>
       </c>
-      <c r="Y72" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="inlineStr">
+      <c r="Z72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="inlineStr">
         <is>
           <t>privacy legislation, compliance governance, policy management, codes of ethics, regulatory documentation</t>
         </is>
       </c>
-      <c r="AA72" t="b">
+      <c r="AB72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9698,18 +10102,23 @@
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>Develops, records and submits review and grievance procedures to designated personnel.</t>
         </is>
       </c>
-      <c r="Y73" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="inlineStr">
+      <c r="Z73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="inlineStr">
         <is>
           <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
         </is>
       </c>
-      <c r="AA73" t="b">
+      <c r="AB73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9820,18 +10229,23 @@
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
           <t>Sequences and schedules complex activities, monitors progress and coordinates communication to maintain delivery momentum.</t>
         </is>
       </c>
-      <c r="Y74" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z74" t="inlineStr">
+      <c r="Z74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="inlineStr">
         <is>
           <t>scheduling, resource allocation, stakeholder communication, project monitoring, Gantt charts</t>
         </is>
       </c>
-      <c r="AA74" t="b">
+      <c r="AB74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9942,18 +10356,23 @@
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
           <t>Monitors and analyses legislative changes to ensure ongoing compliance with rights and responsibilities.</t>
         </is>
       </c>
-      <c r="Y75" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z75" t="inlineStr">
+      <c r="Z75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="inlineStr">
         <is>
           <t>compliance, legislation monitoring, regulatory analysis, policy tracking, legal research</t>
         </is>
       </c>
-      <c r="AA75" t="b">
+      <c r="AB75" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10064,18 +10483,23 @@
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
           <t>Manages digital information securely by lawfully collecting, storing, accessing and sharing data using compliant systems.</t>
         </is>
       </c>
-      <c r="Y76" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="inlineStr">
+      <c r="Z76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="inlineStr">
         <is>
           <t>cyber security, data protection, information governance, privacy compliance, access control</t>
         </is>
       </c>
-      <c r="AA76" t="b">
+      <c r="AB76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10186,18 +10610,23 @@
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
           <t>Distributes updated policies to stakeholders in accordance with organisational protocols.</t>
         </is>
       </c>
-      <c r="Y77" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="inlineStr">
+      <c r="Z77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="inlineStr">
         <is>
           <t>policy dissemination, stakeholder engagement, communication protocols, change management, organisational compliance</t>
         </is>
       </c>
-      <c r="AA77" t="b">
+      <c r="AB77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10308,18 +10737,23 @@
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
           <t>Engages in verbal idea exchange, actively listening and questioning to draw out others’ views.</t>
         </is>
       </c>
-      <c r="Y78" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="inlineStr">
+      <c r="Z78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="inlineStr">
         <is>
           <t>active listening, questioning techniques, stakeholder engagement, dialogue facilitation, interpersonal communication</t>
         </is>
       </c>
-      <c r="AA78" t="b">
+      <c r="AB78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10437,18 +10871,23 @@
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
           <t>Installs and configures blockchain platform components in line with approved design specifications.</t>
         </is>
       </c>
-      <c r="Y79" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="inlineStr">
+      <c r="Z79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="inlineStr">
         <is>
           <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
         </is>
       </c>
-      <c r="AA79" t="b">
+      <c r="AB79" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10566,18 +11005,23 @@
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
           <t>Identifies and resolves blockchain anomalies through contextual analysis to detect subtle deviations.</t>
         </is>
       </c>
-      <c r="Y80" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="inlineStr">
+      <c r="Z80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="inlineStr">
         <is>
           <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
         </is>
       </c>
-      <c r="AA80" t="b">
+      <c r="AB80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10695,18 +11139,23 @@
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
           <t>Defines blockchain objectives and requirements aligned with organisational needs in hybrid environments.</t>
         </is>
       </c>
-      <c r="Y81" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="inlineStr">
+      <c r="Z81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="inlineStr">
         <is>
           <t>distributed ledger, use‑case definition, stakeholder analysis, smart contract design, governance frameworks</t>
         </is>
       </c>
-      <c r="AA81" t="b">
+      <c r="AB81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10824,18 +11273,23 @@
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
           <t>Implements consensus mechanisms by configuring and deploying required system components.</t>
         </is>
       </c>
-      <c r="Y82" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="inlineStr">
+      <c r="Z82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="inlineStr">
         <is>
           <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
         </is>
       </c>
-      <c r="AA82" t="b">
+      <c r="AB82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10953,18 +11407,23 @@
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
           <t>Produces detailed design documentation aligned with organisational requirements to support project delivery.</t>
         </is>
       </c>
-      <c r="Y83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="inlineStr">
+      <c r="Z83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="inlineStr">
         <is>
           <t>technical specifications, design standards, engineering documentation, organisational requirements</t>
         </is>
       </c>
-      <c r="AA83" t="b">
+      <c r="AB83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11082,18 +11541,23 @@
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
           <t>Submits documentation for review, seeks feedback and incorporates approved amendments.</t>
         </is>
       </c>
-      <c r="Y84" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="inlineStr">
+      <c r="Z84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA84" t="inlineStr">
         <is>
           <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
         </is>
       </c>
-      <c r="AA84" t="b">
+      <c r="AB84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11211,18 +11675,23 @@
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
           <t>Designs integration workflows by mapping data flows and configuring tools to meet organisational needs.</t>
         </is>
       </c>
-      <c r="Y85" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="inlineStr">
+      <c r="Z85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA85" t="inlineStr">
         <is>
           <t>systems integration, workflow orchestration, process automation, ETL, API middleware</t>
         </is>
       </c>
-      <c r="AA85" t="b">
+      <c r="AB85" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11335,23 +11804,28 @@
         <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr">
         <is>
+          <t>keep:3, "Maintenance Schedule Development":1, "Maintenance Schedule Documentation":1</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
           <t>Develops and records maintenance schedules aligned with equipment requirements and timelines.</t>
         </is>
       </c>
-      <c r="Y86" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z86" t="inlineStr">
+      <c r="Z86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA86" t="inlineStr">
         <is>
           <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
         </is>
       </c>
-      <c r="AA86" t="b">
+      <c r="AB86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11466,21 +11940,30 @@
       <c r="V87" t="n">
         <v>0.9</v>
       </c>
-      <c r="W87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/5: </t>
+        </is>
+      </c>
       <c r="X87" t="inlineStr">
         <is>
+          <t>keep:2, "Maintenance Testing":3</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
           <t>Plans, selects and conducts maintenance tests to verify equipment functionality and compliance.</t>
         </is>
       </c>
-      <c r="Y87" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="inlineStr">
+      <c r="Z87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="inlineStr">
         <is>
           <t>preventive maintenance, test procedures, equipment inspection, reliability testing, compliance standards</t>
         </is>
       </c>
-      <c r="AA87" t="b">
+      <c r="AB87" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11598,18 +12081,23 @@
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>Selects and configures security platforms for blockchain solutions based on risk assessments.</t>
         </is>
       </c>
-      <c r="Y88" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z88" t="inlineStr">
+      <c r="Z88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA88" t="inlineStr">
         <is>
           <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
         </is>
       </c>
-      <c r="AA88" t="b">
+      <c r="AB88" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11727,18 +12215,23 @@
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
           <t>Deploys and manages smart contracts on approved blockchain platforms in line with solution specifications.</t>
         </is>
       </c>
-      <c r="Y89" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="inlineStr">
+      <c r="Z89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="inlineStr">
         <is>
           <t>blockchain, Ethereum, Solidity, decentralised applications, Web3</t>
         </is>
       </c>
-      <c r="AA89" t="b">
+      <c r="AB89" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11856,18 +12349,23 @@
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
           <t>Diagnoses and resolves blockchain solution issues and optimises performance for scalable deployment.</t>
         </is>
       </c>
-      <c r="Y90" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="inlineStr">
+      <c r="Z90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA90" t="inlineStr">
         <is>
           <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
         </is>
       </c>
-      <c r="AA90" t="b">
+      <c r="AB90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11985,18 +12483,23 @@
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
           <t>Tests and evaluates solutions against organisational requirements to confirm suitability.</t>
         </is>
       </c>
-      <c r="Y91" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="inlineStr">
+      <c r="Z91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA91" t="inlineStr">
         <is>
           <t>benchmarking, requirements compliance, load testing, service level agreements, performance metrics</t>
         </is>
       </c>
-      <c r="AA91" t="b">
+      <c r="AB91" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12114,18 +12617,23 @@
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
           <t>Engages stakeholders to clarify requirements and accountabilities using appropriate industry terminology.</t>
         </is>
       </c>
-      <c r="Y92" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="inlineStr">
+      <c r="Z92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="inlineStr">
         <is>
           <t>stakeholder engagement, requirements gathering, industry terminology, verbal communication, active listening</t>
         </is>
       </c>
-      <c r="AA92" t="b">
+      <c r="AB92" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12243,18 +12751,23 @@
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
           <t>Analyses hybrid environments to identify organisational use cases aligned with business needs.</t>
         </is>
       </c>
-      <c r="Y93" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="inlineStr">
+      <c r="Z93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="inlineStr">
         <is>
           <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, functional requirements</t>
         </is>
       </c>
-      <c r="AA93" t="b">
+      <c r="AB93" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12372,21 +12885,30 @@
       <c r="V94" t="n">
         <v>0.9</v>
       </c>
-      <c r="W94" t="inlineStr"/>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X94" t="inlineStr">
         <is>
+          <t>keep:0, "Data Log Ingestion":5</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
           <t>Ingests data logs into analytics platforms as instructed to support monitoring and analysis.</t>
         </is>
       </c>
-      <c r="Y94" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z94" t="inlineStr">
+      <c r="Z94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA94" t="inlineStr">
         <is>
           <t>data ingestion, log analytics, ETL pipelines, analytics platforms, monitoring</t>
         </is>
       </c>
-      <c r="AA94" t="b">
+      <c r="AB94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12511,18 +13033,23 @@
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
           <t>Identifies relevant legislation and internal policies governing the collection, analysis and use of threat data.</t>
         </is>
       </c>
-      <c r="Y95" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z95" t="inlineStr">
+      <c r="Z95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="inlineStr">
         <is>
           <t>regulatory compliance, legislation, policy analysis, threat intelligence, risk assessment</t>
         </is>
       </c>
-      <c r="AA95" t="b">
+      <c r="AB95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12643,18 +13170,23 @@
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
           <t>Examines datasets to identify, document and resolve data discrepancies and inconsistencies.</t>
         </is>
       </c>
-      <c r="Y96" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z96" t="inlineStr">
+      <c r="Z96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="inlineStr">
         <is>
           <t>data validation, anomaly detection, data quality, data auditing, profiling</t>
         </is>
       </c>
-      <c r="AA96" t="b">
+      <c r="AB96" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12770,23 +13302,32 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W97" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>postprocess: spelling/redundancy</t>
+        </is>
+      </c>
       <c r="X97" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
           <t>Compiles alerts, logs and event reports into structured datasets in line with organisational policies.</t>
         </is>
       </c>
-      <c r="Y97" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z97" t="inlineStr">
+      <c r="Z97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA97" t="inlineStr">
         <is>
           <t>log analysis, data ingestion, security monitoring, data governance, ETL processes</t>
         </is>
       </c>
-      <c r="AA97" t="b">
+      <c r="AB97" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12908,21 +13449,30 @@
       <c r="V98" t="n">
         <v>0.9</v>
       </c>
-      <c r="W98" t="inlineStr"/>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X98" t="inlineStr">
         <is>
+          <t>keep:0, "False Data Detection":5</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
           <t>Reviews test results to identify and correct false positives and false negatives.</t>
         </is>
       </c>
-      <c r="Y98" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z98" t="inlineStr">
+      <c r="Z98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="inlineStr">
         <is>
           <t>type I error, anomaly detection, validation testing, precision‑recall analysis, statistical significance</t>
         </is>
       </c>
-      <c r="AA98" t="b">
+      <c r="AB98" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13039,18 +13589,23 @@
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
           <t>Produces formal investigation reports outlining findings and recommendations in accordance with organisational procedures.</t>
         </is>
       </c>
-      <c r="Y99" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z99" t="inlineStr">
+      <c r="Z99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA99" t="inlineStr">
         <is>
           <t>incident reporting, root‑cause analysis, procedural compliance, report writing, safety management</t>
         </is>
       </c>
-      <c r="AA99" t="b">
+      <c r="AB99" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13175,18 +13730,23 @@
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
           <t>Develops and validates mitigation strategies, action steps and lessons learned with relevant personnel.</t>
         </is>
       </c>
-      <c r="Y100" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z100" t="inlineStr">
+      <c r="Z100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA100" t="inlineStr">
         <is>
           <t>risk management, lessons learned, action planning, stakeholder engagement, mitigation planning</t>
         </is>
       </c>
-      <c r="AA100" t="b">
+      <c r="AB100" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13304,21 +13864,30 @@
       <c r="V101" t="n">
         <v>0.9</v>
       </c>
-      <c r="W101" t="inlineStr"/>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X101" t="inlineStr">
         <is>
+          <t>keep:0, "Threat Risk Assessment":5</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
           <t>Assesses threats by evaluating likelihood and impact to prioritise risk mitigation actions.</t>
         </is>
       </c>
-      <c r="Y101" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="inlineStr">
+      <c r="Z101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="inlineStr">
         <is>
           <t>risk assessment, probability analysis, threat modelling, impact evaluation, risk matrices</t>
         </is>
       </c>
-      <c r="AA101" t="b">
+      <c r="AB101" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13439,18 +14008,23 @@
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
           <t>Identifies network and data‑source security equipment using system diagrams and technical documentation.</t>
         </is>
       </c>
-      <c r="Y102" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="inlineStr">
+      <c r="Z102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="inlineStr">
         <is>
           <t>cyber security, network security, asset inventories, IDS, firewalls</t>
         </is>
       </c>
-      <c r="AA102" t="b">
+      <c r="AB102" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13571,18 +14145,23 @@
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
           <t>Imports security logs into analytics platforms to support monitoring and threat detection.</t>
         </is>
       </c>
-      <c r="Y103" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z103" t="inlineStr">
+      <c r="Z103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="inlineStr">
         <is>
           <t>log aggregation, SIEM, data ingestion, security analytics, ELK stack</t>
         </is>
       </c>
-      <c r="AA103" t="b">
+      <c r="AB103" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13703,18 +14282,23 @@
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
           <t>Communicates threat findings through structured discussions and reviews with relevant personnel.</t>
         </is>
       </c>
-      <c r="Y104" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z104" t="inlineStr">
+      <c r="Z104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="inlineStr">
         <is>
           <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
         </is>
       </c>
-      <c r="AA104" t="b">
+      <c r="AB104" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13835,18 +14419,23 @@
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
           <t>Collects and structures alerts, logs and event data in accordance with organisational data policies.</t>
         </is>
       </c>
-      <c r="Y105" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z105" t="inlineStr">
+      <c r="Z105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="inlineStr">
         <is>
           <t>threat intelligence, log analysis, SIEM, incident response, security monitoring</t>
         </is>
       </c>
-      <c r="AA105" t="b">
+      <c r="AB105" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13958,21 +14547,30 @@
       <c r="V106" t="n">
         <v>0.9</v>
       </c>
-      <c r="W106" t="inlineStr"/>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/5: </t>
+        </is>
+      </c>
       <c r="X106" t="inlineStr">
         <is>
+          <t>keep:2, "Anomaly Detection":3</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
           <t>Monitors operational data to detect contextual anomalies and resolves deviations in a timely manner.</t>
         </is>
       </c>
-      <c r="Y106" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z106" t="inlineStr">
+      <c r="Z106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="inlineStr">
         <is>
           <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
         </is>
       </c>
-      <c r="AA106" t="b">
+      <c r="AB106" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14087,18 +14685,23 @@
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
           <t>Implements enhanced protection plan requirements and asset management processes to safeguard assets.</t>
         </is>
       </c>
-      <c r="Y107" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z107" t="inlineStr">
+      <c r="Z107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="inlineStr">
         <is>
           <t>asset tracking, risk mitigation, protection plans, maintenance scheduling, capital budgeting</t>
         </is>
       </c>
-      <c r="AA107" t="b">
+      <c r="AB107" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14213,18 +14816,23 @@
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
           <t>Conducts critical infrastructure research to support protection planning and documentation requirements.</t>
         </is>
       </c>
-      <c r="Y108" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z108" t="inlineStr">
+      <c r="Z108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="inlineStr">
         <is>
           <t>infrastructure protection, risk assessment, threat modelling, resilience analysis, policy compliance</t>
         </is>
       </c>
-      <c r="AA108" t="b">
+      <c r="AB108" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14339,18 +14947,23 @@
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
           <t>Executes scheduled data backups in line with organisational policies and procedures.</t>
         </is>
       </c>
-      <c r="Y109" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z109" t="inlineStr">
+      <c r="Z109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA109" t="inlineStr">
         <is>
           <t>disaster recovery, backup software, data retention policies, storage replication, ICT compliance</t>
         </is>
       </c>
-      <c r="AA109" t="b">
+      <c r="AB109" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14465,18 +15078,23 @@
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
           <t>Implements device security controls in accordance with protection plans and technical specifications.</t>
         </is>
       </c>
-      <c r="Y110" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z110" t="inlineStr">
+      <c r="Z110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="inlineStr">
         <is>
           <t>endpoint protection, device hardening, security policies, encryption, mobile device management</t>
         </is>
       </c>
-      <c r="AA110" t="b">
+      <c r="AB110" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14591,18 +15209,23 @@
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
           <t>Submits protection plans for review and incorporates stakeholder feedback to improve outcomes.</t>
         </is>
       </c>
-      <c r="Y111" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z111" t="inlineStr">
+      <c r="Z111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="inlineStr">
         <is>
           <t>stakeholder communication, feedback loops, response management, plan documentation, compliance reporting</t>
         </is>
       </c>
-      <c r="AA111" t="b">
+      <c r="AB111" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14717,18 +15340,23 @@
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
           <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
         </is>
       </c>
-      <c r="Y112" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z112" t="inlineStr">
+      <c r="Z112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="inlineStr">
         <is>
           <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
         </is>
       </c>
-      <c r="AA112" t="b">
+      <c r="AB112" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14843,18 +15471,23 @@
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
           <t>Develops staged operational plans and regularly reviews priorities and performance during execution.</t>
         </is>
       </c>
-      <c r="Y113" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z113" t="inlineStr">
+      <c r="Z113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="inlineStr">
         <is>
           <t>operational planning, performance monitoring, resource allocation, timeline management, Gantt charts</t>
         </is>
       </c>
-      <c r="AA113" t="b">
+      <c r="AB113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14874,7 +15507,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Protection Plan Analysis</t>
+          <t>Critical Infrastructure Protection Analysis</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -14961,26 +15594,35 @@
         </is>
       </c>
       <c r="U114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V114" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W114" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X114" t="inlineStr">
         <is>
+          <t>keep:0, "Critical Infrastructure Protection Analysis":5</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
           <t>Evaluates current critical infrastructure protection plans to identify gaps and recommend improvements.</t>
         </is>
       </c>
-      <c r="Y114" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z114" t="inlineStr">
+      <c r="Z114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA114" t="inlineStr">
         <is>
           <t>critical infrastructure, risk assessment, cyber security resilience, ISO 27001, vulnerability analysis</t>
         </is>
       </c>
-      <c r="AA114" t="b">
+      <c r="AB114" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15095,18 +15737,23 @@
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
           <t>Develops and records critical infrastructure protection plans aligned with organisational policies and procedures.</t>
         </is>
       </c>
-      <c r="Y115" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="inlineStr">
+      <c r="Z115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="inlineStr">
         <is>
           <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
         </is>
       </c>
-      <c r="AA115" t="b">
+      <c r="AB115" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15218,21 +15865,30 @@
       <c r="V116" t="n">
         <v>0.9</v>
       </c>
-      <c r="W116" t="inlineStr"/>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X116" t="inlineStr">
         <is>
+          <t>keep:0, "Protection Plan Testing":5</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
           <t>Conducts protection plan testing to validate safeguards in line with organisational requirements.</t>
         </is>
       </c>
-      <c r="Y116" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="inlineStr">
+      <c r="Z116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="inlineStr">
         <is>
           <t>cyber security, risk assessment, compliance testing, security policies, vulnerability testing</t>
         </is>
       </c>
-      <c r="AA116" t="b">
+      <c r="AB116" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15347,18 +16003,23 @@
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
           <t>Collects, analyses and reports test results for decision‑making purposes.</t>
         </is>
       </c>
-      <c r="Y117" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z117" t="inlineStr">
+      <c r="Z117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA117" t="inlineStr">
         <is>
           <t>data interpretation, performance metrics, compliance reporting, organisational standards, business intelligence</t>
         </is>
       </c>
-      <c r="AA117" t="b">
+      <c r="AB117" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15470,21 +16131,30 @@
       <c r="V118" t="n">
         <v>0.9</v>
       </c>
-      <c r="W118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X118" t="inlineStr">
         <is>
+          <t>keep:0, "Risk Assessment":5</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
           <t>Evaluates protection, vulnerability and risk levels and recommends mitigations aligned with organisational needs.</t>
         </is>
       </c>
-      <c r="Y118" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="inlineStr">
+      <c r="Z118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="inlineStr">
         <is>
           <t>vulnerability analysis, mitigation planning, risk matrices, security governance, ISO 27001 compliance</t>
         </is>
       </c>
-      <c r="AA118" t="b">
+      <c r="AB118" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15599,18 +16269,23 @@
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
           <t>Installs and configures software updates in line with documented technical specifications.</t>
         </is>
       </c>
-      <c r="Y119" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z119" t="inlineStr">
+      <c r="Z119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA119" t="inlineStr">
         <is>
           <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
         </is>
       </c>
-      <c r="AA119" t="b">
+      <c r="AB119" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15725,18 +16400,23 @@
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
           <t>Produces workplace documentation using mandated structure, layout and organisational language standards.</t>
         </is>
       </c>
-      <c r="Y120" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z120" t="inlineStr">
+      <c r="Z120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="inlineStr">
         <is>
           <t>technical writing, process documentation, standard operating procedures, document formatting</t>
         </is>
       </c>
-      <c r="AA120" t="b">
+      <c r="AB120" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15756,7 +16436,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data Type Identification</t>
+          <t>Data Classification Identification</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -15853,26 +16533,31 @@
         </is>
       </c>
       <c r="U121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
           <t>Identifies and categorises data types to inform security architecture requirements.</t>
         </is>
       </c>
-      <c r="Y121" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z121" t="inlineStr">
+      <c r="Z121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="inlineStr">
         <is>
           <t>information security, data inventories, classification schemes, confidentiality levels, security architecture</t>
         </is>
       </c>
-      <c r="AA121" t="b">
+      <c r="AB121" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15993,18 +16678,23 @@
       <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
           <t>Submits required documentation promptly to obtain initial stakeholder feedback.</t>
         </is>
       </c>
-      <c r="Y122" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z122" t="inlineStr">
+      <c r="Z122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="inlineStr">
         <is>
           <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
         </is>
       </c>
-      <c r="AA122" t="b">
+      <c r="AB122" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16121,18 +16811,23 @@
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
           <t>Researches and documents industry‑standard design methodologies to inform security architecture planning.</t>
         </is>
       </c>
-      <c r="Y123" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z123" t="inlineStr">
+      <c r="Z123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="inlineStr">
         <is>
           <t>security architecture, design methodologies, industry standards, security frameworks, risk assessment</t>
         </is>
       </c>
-      <c r="AA123" t="b">
+      <c r="AB123" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16152,7 +16847,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Security Contextual Problem Solving</t>
+          <t>Problem Solving in Security</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -16252,23 +16947,32 @@
         <v>1</v>
       </c>
       <c r="V124" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W124" t="inlineStr"/>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>postprocess: spelling/redundancy</t>
+        </is>
+      </c>
       <c r="X124" t="inlineStr">
         <is>
+          <t>keep:3, "Security Contextual Problem Solving":2</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
           <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
         </is>
       </c>
-      <c r="Y124" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z124" t="inlineStr">
+      <c r="Z124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="inlineStr">
         <is>
           <t>anomaly detection, threat analysis, security monitoring, pattern recognition, situational awareness</t>
         </is>
       </c>
-      <c r="AA124" t="b">
+      <c r="AB124" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16386,21 +17090,30 @@
       <c r="V125" t="n">
         <v>0.9</v>
       </c>
-      <c r="W125" t="inlineStr"/>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X125" t="inlineStr">
         <is>
+          <t>keep:0, "Security Requirements Documentation":5</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
           <t>Documents and validates security architecture findings with relevant personnel.</t>
         </is>
       </c>
-      <c r="Y125" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z125" t="inlineStr">
+      <c r="Z125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="inlineStr">
         <is>
           <t>security architecture, risk assessment, compliance frameworks, ISO 27001, threat modelling</t>
         </is>
       </c>
-      <c r="AA125" t="b">
+      <c r="AB125" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16521,18 +17234,23 @@
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
           <t>Prepares and delivers documented security architecture presentations for stakeholder engagement.</t>
         </is>
       </c>
-      <c r="Y126" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="inlineStr">
+      <c r="Z126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="inlineStr">
         <is>
           <t>information security, enterprise architecture, risk assessment, security frameworks, technical presentations</t>
         </is>
       </c>
-      <c r="AA126" t="b">
+      <c r="AB126" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16653,18 +17371,23 @@
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
           <t>Validates security designs using industry‑recognised methodologies.</t>
         </is>
       </c>
-      <c r="Y127" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z127" t="inlineStr">
+      <c r="Z127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="inlineStr">
         <is>
           <t>security architecture, threat modelling, NIST framework, ISO 27001, risk assessment</t>
         </is>
       </c>
-      <c r="AA127" t="b">
+      <c r="AB127" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16789,18 +17512,23 @@
       <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
           <t>Assesses assets to determine required security levels, perimeters, features and protection modes.</t>
         </is>
       </c>
-      <c r="Y128" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="inlineStr">
+      <c r="Z128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="inlineStr">
         <is>
           <t>risk assessment, access control, security architecture, perimeter security, security policy</t>
         </is>
       </c>
-      <c r="AA128" t="b">
+      <c r="AB128" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16925,18 +17653,23 @@
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
           <t>Develops staged operational plans for security initiatives and reviews progress during delivery.</t>
         </is>
       </c>
-      <c r="Y129" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="inlineStr">
+      <c r="Z129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="inlineStr">
         <is>
           <t>cyber security governance, risk assessment, phased implementation, performance monitoring, project scheduling tools</t>
         </is>
       </c>
-      <c r="AA129" t="b">
+      <c r="AB129" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17053,18 +17786,23 @@
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
           <t>Analyses organisational operations and infrastructure to identify specific security requirements.</t>
         </is>
       </c>
-      <c r="Y130" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z130" t="inlineStr">
+      <c r="Z130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="inlineStr">
         <is>
           <t>risk assessment, threat modelling, security architecture, compliance standards, vulnerability analysis</t>
         </is>
       </c>
-      <c r="AA130" t="b">
+      <c r="AB130" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17189,18 +17927,23 @@
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
           <t>Designs and documents security solutions aligned with organisational standards and requirements.</t>
         </is>
       </c>
-      <c r="Y131" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z131" t="inlineStr">
+      <c r="Z131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="inlineStr">
         <is>
           <t>cyber security architecture, risk assessment, security compliance, solution documentation, threat modelling</t>
         </is>
       </c>
-      <c r="AA131" t="b">
+      <c r="AB131" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17325,18 +18068,23 @@
       <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
           <t>Produces detailed technical documentation outlining findings and proposed solutions.</t>
         </is>
       </c>
-      <c r="Y132" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="inlineStr">
+      <c r="Z132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="inlineStr">
         <is>
           <t>technical writing, documentation standards, reporting and analysis, knowledge management</t>
         </is>
       </c>
-      <c r="AA132" t="b">
+      <c r="AB132" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17457,18 +18205,23 @@
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
           <t>Reviews technical, manufacturer and organisational documentation to confirm job requirements prior to work commencement.</t>
         </is>
       </c>
-      <c r="Y133" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="inlineStr">
+      <c r="Z133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="inlineStr">
         <is>
           <t>technical documentation, specification standards, manufacturer manuals, job requirement analysis, engineering drawings</t>
         </is>
       </c>
-      <c r="AA133" t="b">
+      <c r="AB133" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17606,18 +18359,23 @@
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
           <t>Makes independent strategic decisions to align actions with organisational objectives and improve performance.</t>
         </is>
       </c>
-      <c r="Y134" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="inlineStr">
+      <c r="Z134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="inlineStr">
         <is>
           <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
         </is>
       </c>
-      <c r="AA134" t="b">
+      <c r="AB134" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17751,18 +18509,23 @@
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
           <t>Designs and implements forensic evidence collection processes to preserve data during incident response.</t>
         </is>
       </c>
-      <c r="Y135" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z135" t="inlineStr">
+      <c r="Z135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="inlineStr">
         <is>
           <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
         </is>
       </c>
-      <c r="AA135" t="b">
+      <c r="AB135" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17892,18 +18655,23 @@
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
           <t>Prepares detailed incident reports documenting response actions against task requirements.</t>
         </is>
       </c>
-      <c r="Y136" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z136" t="inlineStr">
+      <c r="Z136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="inlineStr">
         <is>
           <t>security incident response, incident reporting, ITIL, SIEM, compliance documentation</t>
         </is>
       </c>
-      <c r="AA136" t="b">
+      <c r="AB136" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17923,7 +18691,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Incident Response Evaluation</t>
+          <t>Response Plan Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -18029,26 +18797,35 @@
         </is>
       </c>
       <c r="U137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V137" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W137" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X137" t="inlineStr">
         <is>
+          <t>keep:0, "Response Plan Evaluation":5</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
           <t>Evaluates incident response plans for effectiveness across hybrid operating environments.</t>
         </is>
       </c>
-      <c r="Y137" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="inlineStr">
+      <c r="Z137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="inlineStr">
         <is>
           <t>security operations, post‑incident analysis, efficiency metrics, response plan documentation, SOC tools</t>
         </is>
       </c>
-      <c r="AA137" t="b">
+      <c r="AB137" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18182,18 +18959,23 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
           <t>Develops and records incident response plans aligned with organisational requirements.</t>
         </is>
       </c>
-      <c r="Y138" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z138" t="inlineStr">
+      <c r="Z138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="inlineStr">
         <is>
           <t>cyber security, incident handling, NIST framework, playbook development, risk management</t>
         </is>
       </c>
-      <c r="AA138" t="b">
+      <c r="AB138" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18323,18 +19105,23 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
           <t>Documents incident response team roles and services to support coordinated response.</t>
         </is>
       </c>
-      <c r="Y139" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="inlineStr">
+      <c r="Z139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="inlineStr">
         <is>
           <t>incident response, service documentation, team coordination, organisational compliance, ticketing systems</t>
         </is>
       </c>
-      <c r="AA139" t="b">
+      <c r="AB139" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18465,21 +19252,30 @@
       <c r="V140" t="n">
         <v>0.9</v>
       </c>
-      <c r="W140" t="inlineStr"/>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X140" t="inlineStr">
         <is>
+          <t>keep:0, "Incident Response Training":5</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
           <t>Designs and conducts red‑team exercises and incident response simulations, including staffing and training plans.</t>
         </is>
       </c>
-      <c r="Y140" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="inlineStr">
+      <c r="Z140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="inlineStr">
         <is>
           <t>adversary simulation, incident response planning, threat modelling, security training programmes, MITRE ATT&amp;CK framework</t>
         </is>
       </c>
-      <c r="AA140" t="b">
+      <c r="AB140" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18499,7 +19295,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Communication Effectiveness Assessment</t>
+          <t>Response Communication Assessment</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -18605,26 +19401,31 @@
         </is>
       </c>
       <c r="U141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
           <t>Evaluates the effectiveness of incident response communications across internal and external stakeholders.</t>
         </is>
       </c>
-      <c r="Y141" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z141" t="inlineStr">
+      <c r="Z141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA141" t="inlineStr">
         <is>
           <t>incident response, stakeholder communication, internal coordination, external liaison, communication effectiveness</t>
         </is>
       </c>
-      <c r="AA141" t="b">
+      <c r="AB141" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18644,7 +19445,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Risk Analysis</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -18754,26 +19555,31 @@
         </is>
       </c>
       <c r="U142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
           <t>Interprets and documents numerical and technical system data to support risk assessment.</t>
         </is>
       </c>
-      <c r="Y142" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z142" t="inlineStr">
+      <c r="Z142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="inlineStr">
         <is>
           <t>quantitative analysis, technical data interpretation, risk assessment, system modelling, data documentation</t>
         </is>
       </c>
-      <c r="AA142" t="b">
+      <c r="AB142" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18911,18 +19717,23 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
           <t>Executes incident response actions in accordance with approved incident response plans.</t>
         </is>
       </c>
-      <c r="Y143" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z143" t="inlineStr">
+      <c r="Z143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA143" t="inlineStr">
         <is>
           <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
         </is>
       </c>
-      <c r="AA143" t="b">
+      <c r="AB143" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19060,18 +19871,23 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
           <t>Develops and documents incident management policies aligned with organisational specifications.</t>
         </is>
       </c>
-      <c r="Y144" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z144" t="inlineStr">
+      <c r="Z144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="inlineStr">
         <is>
           <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
         </is>
       </c>
-      <c r="AA144" t="b">
+      <c r="AB144" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19209,18 +20025,23 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
           <t>Analyses and records numerical system data to inform technical decision‑making.</t>
         </is>
       </c>
-      <c r="Y145" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z145" t="inlineStr">
+      <c r="Z145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="inlineStr">
         <is>
           <t>quantitative analysis, technical system data, measurement instrumentation, data documentation, engineering diagnostics</t>
         </is>
       </c>
-      <c r="AA145" t="b">
+      <c r="AB145" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19347,18 +20168,23 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
           <t>Assesses system impacts on business continuity to identify risks and mitigation strategies.</t>
         </is>
       </c>
-      <c r="Y146" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z146" t="inlineStr">
+      <c r="Z146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA146" t="inlineStr">
         <is>
           <t>business continuity, risk assessment, impact analysis, disaster recovery, resilience planning</t>
         </is>
       </c>
-      <c r="AA146" t="b">
+      <c r="AB146" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19485,18 +20311,23 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
           <t>Designs and implements compliance strategies to align organisational processes with regulatory requirements.</t>
         </is>
       </c>
-      <c r="Y147" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z147" t="inlineStr">
+      <c r="Z147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="inlineStr">
         <is>
           <t>regulatory compliance, policy enforcement, risk management, governance, audit</t>
         </is>
       </c>
-      <c r="AA147" t="b">
+      <c r="AB147" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19627,18 +20458,23 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
           <t>Develops contingency plans by identifying threats and defining response actions.</t>
         </is>
       </c>
-      <c r="Y148" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z148" t="inlineStr">
+      <c r="Z148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA148" t="inlineStr">
         <is>
           <t>risk assessment, business continuity, threat identification, mitigation strategies, scenario analysis</t>
         </is>
       </c>
-      <c r="AA148" t="b">
+      <c r="AB148" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19765,18 +20601,23 @@
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
           <t>Evaluates prevention and recovery options for compliance and cost effectiveness.</t>
         </is>
       </c>
-      <c r="Y149" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z149" t="inlineStr">
+      <c r="Z149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA149" t="inlineStr">
         <is>
           <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, financial modelling</t>
         </is>
       </c>
-      <c r="AA149" t="b">
+      <c r="AB149" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19903,18 +20744,23 @@
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
           <t>Develops comprehensive disaster recovery plans detailing procedures, resources and recovery timeframes.</t>
         </is>
       </c>
-      <c r="Y150" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z150" t="inlineStr">
+      <c r="Z150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="inlineStr">
         <is>
           <t>business continuity, backup and restore, recovery time objectives, risk assessment, disaster recovery testing</t>
         </is>
       </c>
-      <c r="AA150" t="b">
+      <c r="AB150" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20041,18 +20887,23 @@
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
           <t>Reviews operational procedures against industry benchmarks to verify risk controls.</t>
         </is>
       </c>
-      <c r="Y151" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z151" t="inlineStr">
+      <c r="Z151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA151" t="inlineStr">
         <is>
           <t>compliance, risk management, standard operating procedures, regulatory guidance, audit</t>
         </is>
       </c>
-      <c r="AA151" t="b">
+      <c r="AB151" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20176,21 +21027,30 @@
       <c r="V152" t="n">
         <v>0.9</v>
       </c>
-      <c r="W152" t="inlineStr"/>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X152" t="inlineStr">
         <is>
+          <t>keep:0, "Business Data Analysis/Data Analysis":5</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
           <t>Analyses and documents numerical, financial and technical data to support operational decisions.</t>
         </is>
       </c>
-      <c r="Y152" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z152" t="inlineStr">
+      <c r="Z152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="inlineStr">
         <is>
           <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, data reporting</t>
         </is>
       </c>
-      <c r="AA152" t="b">
+      <c r="AB152" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20317,18 +21177,23 @@
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
           <t>Designs and implements prevention and recovery strategies to strengthen system resilience.</t>
         </is>
       </c>
-      <c r="Y153" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z153" t="inlineStr">
+      <c r="Z153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA153" t="inlineStr">
         <is>
           <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
         </is>
       </c>
-      <c r="AA153" t="b">
+      <c r="AB153" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20459,18 +21324,23 @@
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
           <t>Collects and analyses data, incorporates feedback and refines plans and processes.</t>
         </is>
       </c>
-      <c r="Y154" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z154" t="inlineStr">
+      <c r="Z154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA154" t="inlineStr">
         <is>
           <t>data analysis, feedback loops, process improvement, root‑cause analysis, continuous improvement</t>
         </is>
       </c>
-      <c r="AA154" t="b">
+      <c r="AB154" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20490,7 +21360,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Analysis</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -20589,26 +21459,31 @@
         </is>
       </c>
       <c r="U155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V155" t="n">
-        <v>0.9</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr">
         <is>
+          <t>keep:3, "Risk Assessment":2</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
           <t>Conducts comprehensive risk assessments and develops disaster recovery and contingency solutions.</t>
         </is>
       </c>
-      <c r="Y155" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z155" t="inlineStr">
+      <c r="Z155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="inlineStr">
         <is>
           <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
         </is>
       </c>
-      <c r="AA155" t="b">
+      <c r="AB155" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20735,18 +21610,23 @@
       <c r="W156" t="inlineStr"/>
       <c r="X156" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
           <t>Engages stakeholders through timely document submission, feedback collection and response.</t>
         </is>
       </c>
-      <c r="Y156" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z156" t="inlineStr">
+      <c r="Z156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA156" t="inlineStr">
         <is>
           <t>stakeholder engagement, feedback loops, document management, communication protocols, collaboration tools</t>
         </is>
       </c>
-      <c r="AA156" t="b">
+      <c r="AB156" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20873,18 +21753,23 @@
       <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
           <t>Develops and aligns hybrid work priorities and outcomes through structured strategic planning.</t>
         </is>
       </c>
-      <c r="Y157" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z157" t="inlineStr">
+      <c r="Z157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="inlineStr">
         <is>
           <t>priority alignment, outcome mapping, roadmap development, performance metrics, scenario analysis</t>
         </is>
       </c>
-      <c r="AA157" t="b">
+      <c r="AB157" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21011,18 +21896,23 @@
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
           <t>Collaborates with team members using communication tools and strategies to maintain effective working relationships.</t>
         </is>
       </c>
-      <c r="Y158" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z158" t="inlineStr">
+      <c r="Z158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA158" t="inlineStr">
         <is>
           <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, interpersonal communication</t>
         </is>
       </c>
-      <c r="AA158" t="b">
+      <c r="AB158" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21149,18 +22039,23 @@
       <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
           <t>Prepares evaluation and strategy documents outlining findings and recommendations for stakeholders.</t>
         </is>
       </c>
-      <c r="Y159" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z159" t="inlineStr">
+      <c r="Z159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA159" t="inlineStr">
         <is>
           <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
         </is>
       </c>
-      <c r="AA159" t="b">
+      <c r="AB159" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21287,18 +22182,23 @@
       <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr">
         <is>
+          <t>keep:5</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
           <t>Assesses system vulnerabilities through structured threat identification and analysis to support mitigation planning.</t>
         </is>
       </c>
-      <c r="Y160" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z160" t="inlineStr">
+      <c r="Z160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA160" t="inlineStr">
         <is>
           <t>risk analysis, vulnerability assessment, threat modelling, cyber security, intelligence gathering</t>
         </is>
       </c>
-      <c r="AA160" t="b">
+      <c r="AB160" t="b">
         <v>0</v>
       </c>
     </row>
